--- a/docs/原生App殼接口文檔_v0.2.xlsx
+++ b/docs/原生App殼接口文檔_v0.2.xlsx
@@ -2416,7 +2416,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>我們和客戶（待定事項 #4）；圖示由 Navy</t>
+          <t>我們和客戶（待定事項 #4）；圖示由設計負責人（待定）</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
